--- a/artfynd/A 43900-2021 artfynd.xlsx
+++ b/artfynd/A 43900-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43900-2021 artfynd.xlsx
+++ b/artfynd/A 43900-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96871478</v>
+        <v>96957408</v>
       </c>
       <c r="B2" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656822.9079626615</v>
+        <v>656933</v>
       </c>
       <c r="R2" t="n">
-        <v>6571387.864240355</v>
+        <v>6571444</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -789,56 +774,43 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Ljungberg</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96957355</v>
+        <v>96871478</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -847,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656872.1952691643</v>
+        <v>656823</v>
       </c>
       <c r="R3" t="n">
-        <v>6571349.450326251</v>
+        <v>6571388</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,22 +849,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,44 +880,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Bo Ljungberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96957408</v>
+        <v>96871535</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656932.8906358009</v>
+        <v>656825</v>
       </c>
       <c r="R4" t="n">
-        <v>6571444.631317091</v>
+        <v>6571336</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,22 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-11-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1034,10 +986,432 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Bo Ljungberg, Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112128198</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92564</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skansberg, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>656802</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6571371</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Bo Törnquist</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96871594</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skansberg, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>656857</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6571538</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal tall intill vägkanten.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bo Ljungberg, Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96871456</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skansberg, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>656799</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6571429</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Bo Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96957355</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skansberg, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>656872</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6571350</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-11-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43900-2021 artfynd.xlsx
+++ b/artfynd/A 43900-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96957408</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96871478</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96871535</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128198</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96871594</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96871456</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1412,8 +1447,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96957355</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>